--- a/examples/Micron DCF.xlsx
+++ b/examples/Micron DCF.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0349B4-D905-4046-9356-493B56726905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFA46C7-F716-AF4A-A0C7-D9A7C24D8A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>Beta</t>
   </si>
   <si>
-    <t>Judgment. 5-year monthly regression against the S&amp;P 500 gives 2.35, pushed up by the 2026 memory surge. 1.6 is closer to other chip makers</t>
-  </si>
-  <si>
     <t>Equity risk premium</t>
   </si>
   <si>
@@ -313,6 +310,9 @@
   </si>
   <si>
     <t>Sources: Micron FY2026 Form 10-K (filed 9 Oct 2026) and 10-Q filings via SEC EDGAR; analyst estimates and price from Yahoo Finance, 14 Oct 2026.</t>
+  </si>
+  <si>
+    <t>Judgment. 5-year monthly regression against the S&amp;P 500 gives 2.35, pushed up by the 2026 memory surge. Blended toward 1: 0.67 × 2.35 + 0.33 = 1.90</t>
   </si>
 </sst>
 </file>
@@ -822,204 +822,204 @@
         <v>17</v>
       </c>
       <c r="C13" s="8">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="9">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="P14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="7">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="10">
         <f>C12+C13*C14+C15</f>
-        <v>0.1239</v>
+        <v>0.13739999999999999</v>
       </c>
       <c r="P16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="7">
         <v>6.2E-2</v>
       </c>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7">
         <v>0.21</v>
       </c>
       <c r="P18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="11">
         <f>C11/(C11+C7*C8)</f>
         <v>4.9825592052284888E-3</v>
       </c>
       <c r="P19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="12">
         <f>C16*(1-C19)+C17*(1-C18)*C19</f>
-        <v>0.12352670666434427</v>
+        <v>0.13695944211507369</v>
       </c>
       <c r="P20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="9">
         <v>0.16</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="9">
         <v>0.1</v>
       </c>
       <c r="P22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="7">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="7">
         <v>0.15</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="9">
         <v>0.35</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="7">
         <v>0.16</v>
       </c>
       <c r="P26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D30" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="F30" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="G30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="I30" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="J30" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="K30" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="L30" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="M30" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="M30" s="13" t="s">
+      <c r="N30" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="O30" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E31" s="9">
         <v>3.28</v>
@@ -1056,12 +1056,12 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="6">
         <f>C9</f>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="11">
         <f>(1773+2169+3654+6136)/(8053+9301+11315+13643)</f>
@@ -1155,12 +1155,12 @@
         <v>0.35</v>
       </c>
       <c r="P33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="6">
         <f t="shared" ref="E34:O34" si="1">E32*E33</f>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" s="6">
         <f t="shared" ref="E35:N35" si="2">E34*(1-$C$21)</f>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E36" s="6">
         <f t="shared" ref="E36:N36" si="3">-E32*$C$22</f>
@@ -1305,12 +1305,12 @@
         <v>-12618.373777275612</v>
       </c>
       <c r="P36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="14">
         <f t="shared" ref="E37:O37" si="4">E35+E36</f>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E38" s="11">
         <f>(DATE(2026,12,31)-$C$6)/365</f>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="15">
         <f>E38/2</f>
@@ -1440,147 +1440,147 @@
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="16">
         <f t="shared" ref="E40:N40" si="5">1/(1+$C$20)^E39</f>
-        <v>0.98763210321025574</v>
+        <v>0.98637870539313777</v>
       </c>
       <c r="F40" s="16">
         <f t="shared" si="5"/>
-        <v>0.92023489289909155</v>
+        <v>0.91246221488541324</v>
       </c>
       <c r="G40" s="16">
         <f t="shared" si="5"/>
-        <v>0.81905920655076481</v>
+        <v>0.80254596697659619</v>
       </c>
       <c r="H40" s="16">
         <f t="shared" si="5"/>
-        <v>0.72900733172821708</v>
+        <v>0.70587035671530063</v>
       </c>
       <c r="I40" s="16">
         <f t="shared" si="5"/>
-        <v>0.64885625540008585</v>
+        <v>0.62084040166127419</v>
       </c>
       <c r="J40" s="16">
         <f t="shared" si="5"/>
-        <v>0.57751742931548578</v>
+        <v>0.54605325279354844</v>
       </c>
       <c r="K40" s="16">
         <f t="shared" si="5"/>
-        <v>0.51402198620635031</v>
+        <v>0.48027504989776187</v>
       </c>
       <c r="L40" s="16">
         <f t="shared" si="5"/>
-        <v>0.4575075814018148</v>
+        <v>0.42242056498014668</v>
       </c>
       <c r="M40" s="16">
         <f t="shared" si="5"/>
-        <v>0.40720668114789732</v>
+        <v>0.37153529785928169</v>
       </c>
       <c r="N40" s="16">
         <f t="shared" si="5"/>
-        <v>0.36243613857374118</v>
+        <v>0.32677972854345483</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="14">
         <f t="shared" ref="E41:N41" si="6">E37*E38*E40</f>
-        <v>21220.407379908702</v>
+        <v>21193.476691647476</v>
       </c>
       <c r="F41" s="14">
         <f t="shared" si="6"/>
-        <v>142820.94721919505</v>
+        <v>141614.62343718097</v>
       </c>
       <c r="G41" s="14">
         <f t="shared" si="6"/>
-        <v>101742.7105153544</v>
+        <v>99691.452510770585</v>
       </c>
       <c r="H41" s="14">
         <f t="shared" si="6"/>
-        <v>42498.819929359648</v>
+        <v>41150.007521049585</v>
       </c>
       <c r="I41" s="14">
         <f t="shared" si="6"/>
-        <v>26125.261165410968</v>
+        <v>24997.243226758121</v>
       </c>
       <c r="J41" s="14">
         <f t="shared" si="6"/>
-        <v>24415.55154939165</v>
+        <v>23085.348883922208</v>
       </c>
       <c r="K41" s="14">
         <f t="shared" si="6"/>
-        <v>22817.730076905176</v>
+        <v>21319.684265100623</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="6"/>
-        <v>21121.384244113833</v>
+        <v>19501.550199941543</v>
       </c>
       <c r="M41" s="14">
         <f t="shared" si="6"/>
-        <v>19363.158563472054</v>
+        <v>17666.942163365926</v>
       </c>
       <c r="N41" s="14">
         <f t="shared" si="6"/>
-        <v>17665.123053891286</v>
+        <v>15927.231039801036</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="6">
         <f>SUM(E41:N41)</f>
-        <v>439791.09369700274</v>
+        <v>426147.55993953813</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="6">
         <f>O37/(C20-C23)</f>
-        <v>640352.96644305997</v>
+        <v>563524.32358077692</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="6">
         <f>D45/(1+C20)^(E38+9)</f>
-        <v>218957.19477858546</v>
+        <v>172701.17314010629</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D47" s="14">
         <f>D44+D46</f>
-        <v>658748.2884755882</v>
+        <v>598848.73307964439</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D48" s="11">
         <f>D46/D47</f>
-        <v>0.33238370195279765</v>
+        <v>0.28838864240719325</v>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D49" s="6">
         <f>C10</f>
@@ -1589,25 +1589,25 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D50" s="14">
         <f>D47+D49</f>
-        <v>727022.2884755882</v>
+        <v>667122.73307964439</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B51" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="17">
         <f>D50/C8</f>
-        <v>642.58643139083267</v>
+        <v>589.64356821605475</v>
       </c>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52" s="18">
         <f>C7</f>
@@ -1616,42 +1616,42 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" s="19">
         <f>D51/D52-1</f>
-        <v>-0.29705136972768353</v>
+        <v>-0.35496749016435869</v>
       </c>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="20">
         <f>C7/74.33</f>
         <v>12.298264496165748</v>
       </c>
       <c r="P54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D55" s="20">
         <f>D51/74.33</f>
-        <v>8.6450481823063736</v>
+        <v>7.9327804145843501</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" s="21">
         <v>0.3</v>
@@ -1672,164 +1672,164 @@
     <row r="60" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C60" s="21">
         <f>$C$20+(-0.03)</f>
-        <v>9.3526706664344275E-2</v>
+        <v>0.10695944211507369</v>
       </c>
       <c r="D60" s="18">
         <f t="shared" ref="D60:H64" si="7">(SUMPRODUCT($E$37:$H$37,$E$38:$H$38,1/(1+$C60)^$E$39:$H$39)+SUMPRODUCT($I$32:$N$32*($I$33:$N$33+D$59-$C$25)*(1-$C$21)+$I$36:$N$36,1/(1+$C60)^$I$39:$N$39)+$O$32*D$59*(1-$C$26)*(1-$C$23/$C$24)/($C60-$C$23)/(1+$C60)^($E$38+9)+$C$10)/$C$8</f>
-        <v>755.72701643038215</v>
+        <v>666.30150664710266</v>
       </c>
       <c r="E60" s="18">
         <f t="shared" si="7"/>
-        <v>796.04257468372771</v>
+        <v>699.11390640036541</v>
       </c>
       <c r="F60" s="18">
         <f t="shared" si="7"/>
-        <v>836.35813293707304</v>
+        <v>731.92630615362771</v>
       </c>
       <c r="G60" s="18">
         <f t="shared" si="7"/>
-        <v>876.67369119041859</v>
+        <v>764.73870590689023</v>
       </c>
       <c r="H60" s="18">
         <f t="shared" si="7"/>
-        <v>916.98924944376404</v>
+        <v>797.55110566015287</v>
       </c>
       <c r="P60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C61" s="21">
         <f>$C$20+(-0.015)</f>
-        <v>0.10852670666434427</v>
+        <v>0.12195944211507369</v>
       </c>
       <c r="D61" s="18">
         <f t="shared" si="7"/>
-        <v>657.75440887987043</v>
+        <v>595.89001750123577</v>
       </c>
       <c r="E61" s="18">
         <f t="shared" si="7"/>
-        <v>689.85024952361164</v>
+        <v>622.80649135041392</v>
       </c>
       <c r="F61" s="18">
         <f t="shared" si="7"/>
-        <v>721.94609016735251</v>
+        <v>649.72296519959184</v>
       </c>
       <c r="G61" s="18">
         <f t="shared" si="7"/>
-        <v>754.04193081109372</v>
+        <v>676.63943904876987</v>
       </c>
       <c r="H61" s="18">
         <f t="shared" si="7"/>
-        <v>786.13777145483459</v>
+        <v>703.55591289794779</v>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C62" s="21">
         <f>$C$20+(0)</f>
-        <v>0.12352670666434427</v>
+        <v>0.13695944211507369</v>
       </c>
       <c r="D62" s="18">
         <f t="shared" si="7"/>
-        <v>589.77535789769684</v>
+        <v>544.39716404245269</v>
       </c>
       <c r="E62" s="18">
         <f t="shared" si="7"/>
-        <v>616.18089464426487</v>
+        <v>567.02036612925383</v>
       </c>
       <c r="F62" s="18">
         <f t="shared" si="7"/>
-        <v>642.58643139083267</v>
+        <v>589.64356821605475</v>
       </c>
       <c r="G62" s="18">
         <f t="shared" si="7"/>
-        <v>668.99196813740082</v>
+        <v>612.26677030285578</v>
       </c>
       <c r="H62" s="18">
         <f t="shared" si="7"/>
-        <v>695.39750488396874</v>
+        <v>634.88997238965669</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C63" s="21">
         <f>$C$20+(0.015)</f>
-        <v>0.13852670666434427</v>
+        <v>0.15195944211507367</v>
       </c>
       <c r="D63" s="18">
         <f t="shared" si="7"/>
-        <v>539.8015893827793</v>
+        <v>505.04441482806982</v>
       </c>
       <c r="E63" s="18">
         <f t="shared" si="7"/>
-        <v>562.0429468991108</v>
+        <v>524.40838508548984</v>
       </c>
       <c r="F63" s="18">
         <f t="shared" si="7"/>
-        <v>584.28430441544231</v>
+        <v>543.77235534290969</v>
       </c>
       <c r="G63" s="18">
         <f t="shared" si="7"/>
-        <v>606.5256619317737</v>
+        <v>563.13632560032966</v>
       </c>
       <c r="H63" s="18">
         <f t="shared" si="7"/>
-        <v>628.76701944810509</v>
+        <v>582.50029585774951</v>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C64" s="21">
         <f>$C$20+(0.03)</f>
-        <v>0.15352670666434426</v>
+        <v>0.16695944211507369</v>
       </c>
       <c r="D64" s="18">
         <f t="shared" si="7"/>
-        <v>501.45867065602044</v>
+        <v>473.93136633203528</v>
       </c>
       <c r="E64" s="18">
         <f t="shared" si="7"/>
-        <v>520.52709137114527</v>
+        <v>490.74188437992899</v>
       </c>
       <c r="F64" s="18">
         <f t="shared" si="7"/>
-        <v>539.59551208626988</v>
+        <v>507.55240242782253</v>
       </c>
       <c r="G64" s="18">
         <f t="shared" si="7"/>
-        <v>558.66393280139471</v>
+        <v>524.36292047571624</v>
       </c>
       <c r="H64" s="18">
         <f t="shared" si="7"/>
-        <v>577.73235351651942</v>
+        <v>541.17343852360978</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B66" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
